--- a/data/trans_orig/IP3101-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP3101-Clase-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1447</t>
+          <t>1442</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8326</t>
+          <t>8147</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1302</t>
+          <t>765</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7237</t>
+          <t>6658</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3520</t>
+          <t>3488</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12462</t>
+          <t>11958</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,44%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2854</t>
+          <t>2880</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10913</t>
+          <t>11331</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4027</t>
+          <t>3916</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12237</t>
+          <t>12162</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>8206</t>
+          <t>8262</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>20098</t>
+          <t>20600</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>11,09%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>14507</t>
+          <t>14146</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>27084</t>
+          <t>28120</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>8270</t>
+          <t>8438</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>19128</t>
+          <t>18674</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>25316</t>
+          <t>25640</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>42831</t>
+          <t>43499</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>23,41%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16896</t>
+          <t>17610</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30693</t>
+          <t>31757</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>33,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19176</t>
+          <t>19453</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>33108</t>
+          <t>32955</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,65%</t>
+          <t>36,48%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>40605</t>
+          <t>40333</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>60018</t>
+          <t>60620</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,3%</t>
+          <t>32,63%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>34171</t>
+          <t>34371</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>50254</t>
+          <t>50109</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>35,8%</t>
+          <t>36,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>52,64%</t>
+          <t>52,49%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>33630</t>
+          <t>33921</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>47981</t>
+          <t>48779</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>37,22%</t>
+          <t>37,55%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>53,11%</t>
+          <t>53,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>72714</t>
+          <t>72288</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>94335</t>
+          <t>94564</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>39,13%</t>
+          <t>38,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>50,77%</t>
+          <t>50,89%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>1903</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8921</t>
+          <t>8674</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>808</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6146</t>
+          <t>6967</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3737</t>
+          <t>3809</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12389</t>
+          <t>11936</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,42%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2432</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10147</t>
+          <t>10886</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2753</t>
+          <t>2867</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10514</t>
+          <t>10450</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>6727</t>
+          <t>6582</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>18006</t>
+          <t>18304</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,38%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8881</t>
+          <t>8640</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>19289</t>
+          <t>19581</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8733</t>
+          <t>8600</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>19513</t>
+          <t>19525</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>23,97%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>20513</t>
+          <t>20077</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>35944</t>
+          <t>35329</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>21,97%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13837</t>
+          <t>13933</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26166</t>
+          <t>26233</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>33,05%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10535</t>
+          <t>10175</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21457</t>
+          <t>21267</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>26,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>26761</t>
+          <t>27432</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>44988</t>
+          <t>44478</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>27,65%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>29567</t>
+          <t>28798</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>43246</t>
+          <t>42932</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>37,25%</t>
+          <t>36,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>54,48%</t>
+          <t>54,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>36684</t>
+          <t>36741</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>51229</t>
+          <t>51421</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>45,04%</t>
+          <t>45,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>62,89%</t>
+          <t>63,13%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>69245</t>
+          <t>69557</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>89701</t>
+          <t>90195</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>43,05%</t>
+          <t>43,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>55,77%</t>
+          <t>56,08%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>667</t>
+          <t>663</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6261</t>
+          <t>5049</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,7 +2116,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>562</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6003</t>
+          <t>5845</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1988</t>
+          <t>1984</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9373</t>
+          <t>9007</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,61%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1993</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8753</t>
+          <t>9383</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6676</t>
+          <t>6855</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>17092</t>
+          <t>17032</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>10040</t>
+          <t>10914</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>22333</t>
+          <t>23538</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>14,67%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6228</t>
+          <t>6170</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>16037</t>
+          <t>16076</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>12023</t>
+          <t>11980</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>24134</t>
+          <t>24358</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>20809</t>
+          <t>20974</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>36608</t>
+          <t>36348</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,66%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9928</t>
+          <t>10014</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>20816</t>
+          <t>21574</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>32,9%</t>
+          <t>34,1%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>16971</t>
+          <t>16828</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>29931</t>
+          <t>30180</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>29907</t>
+          <t>29655</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>47399</t>
+          <t>46756</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>29,15%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>24911</t>
+          <t>24333</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>37937</t>
+          <t>37425</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>39,38%</t>
+          <t>38,46%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>59,97%</t>
+          <t>59,16%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>34856</t>
+          <t>34661</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>51147</t>
+          <t>50704</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>35,68%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>52,65%</t>
+          <t>52,19%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>63561</t>
+          <t>64221</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>84122</t>
+          <t>83584</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>39,62%</t>
+          <t>40,03%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>52,44%</t>
+          <t>52,11%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7202</t>
+          <t>7282</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>19056</t>
+          <t>18890</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>9974</t>
+          <t>9872</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>22870</t>
+          <t>22737</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>19962</t>
+          <t>19548</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>35767</t>
+          <t>35554</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,45%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>11618</t>
+          <t>12112</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>24676</t>
+          <t>24982</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>12282</t>
+          <t>12464</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>25581</t>
+          <t>24711</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>27397</t>
+          <t>26895</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>45750</t>
+          <t>44325</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>11,79%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>19570</t>
+          <t>18964</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>35603</t>
+          <t>34050</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>26852</t>
+          <t>26734</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>44435</t>
+          <t>43508</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>50117</t>
+          <t>50794</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>72482</t>
+          <t>72514</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>19,28%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>28921</t>
+          <t>28329</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>45696</t>
+          <t>45675</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>36676</t>
+          <t>37167</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>55368</t>
+          <t>54596</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>29,31%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>70966</t>
+          <t>70524</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>94948</t>
+          <t>96551</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>25,67%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>86461</t>
+          <t>86382</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>108674</t>
+          <t>107954</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>45,54%</t>
+          <t>45,5%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>57,24%</t>
+          <t>56,86%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>62275</t>
+          <t>63634</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>85112</t>
+          <t>84657</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>34,16%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>45,69%</t>
+          <t>45,45%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>155445</t>
+          <t>157081</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>185392</t>
+          <t>186758</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>41,33%</t>
+          <t>41,77%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>49,29%</t>
+          <t>49,66%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3303</t>
+          <t>3482</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>11986</t>
+          <t>12238</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>5956</t>
+          <t>5739</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>15931</t>
+          <t>16064</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>11987</t>
+          <t>11145</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>24593</t>
+          <t>23583</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>10,91%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1894</t>
+          <t>1805</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>9090</t>
+          <t>8883</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>9197</t>
+          <t>9045</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>20707</t>
+          <t>20205</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>12987</t>
+          <t>12800</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>25812</t>
+          <t>26171</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>12,11%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>19194</t>
+          <t>19747</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>33964</t>
+          <t>33076</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>34,66%</t>
+          <t>33,76%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>13134</t>
+          <t>13462</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>26954</t>
+          <t>26436</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>36336</t>
+          <t>36084</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>55520</t>
+          <t>55119</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>25,49%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>9728</t>
+          <t>9784</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>21409</t>
+          <t>21371</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>19776</t>
+          <t>19449</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>34245</t>
+          <t>33942</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>28,71%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>32315</t>
+          <t>32506</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>50939</t>
+          <t>50839</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>23,52%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>37620</t>
+          <t>38347</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>54469</t>
+          <t>54550</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>38,39%</t>
+          <t>39,14%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>55,59%</t>
+          <t>55,67%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>40154</t>
+          <t>39823</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>56402</t>
+          <t>56296</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>33,97%</t>
+          <t>33,69%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>47,71%</t>
+          <t>47,62%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>82426</t>
+          <t>81851</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>106610</t>
+          <t>105148</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>38,13%</t>
+          <t>37,86%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>49,31%</t>
+          <t>48,64%</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>2053</t>
+          <t>2098</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>9589</t>
+          <t>9291</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>1341</t>
+          <t>1324</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>7761</t>
+          <t>7877</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>4717</t>
+          <t>4706</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>13964</t>
+          <t>14153</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,32%</t>
         </is>
       </c>
     </row>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>5637</t>
+          <t>5602</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>15322</t>
+          <t>14892</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4270,12 +4270,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4290,12 +4290,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>1562</t>
+          <t>1897</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>8790</t>
+          <t>8058</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>9223</t>
+          <t>8984</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>20017</t>
+          <t>20726</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>15,11%</t>
         </is>
       </c>
     </row>
@@ -4368,12 +4368,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>12243</t>
+          <t>12677</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>24217</t>
+          <t>24542</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4383,12 +4383,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>33,81%</t>
+          <t>34,26%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4403,12 +4403,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>11790</t>
+          <t>11754</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>23202</t>
+          <t>22823</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>35,41%</t>
+          <t>34,83%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>27530</t>
+          <t>27085</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>43351</t>
+          <t>43636</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>31,81%</t>
         </is>
       </c>
     </row>
@@ -4481,12 +4481,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>7783</t>
+          <t>7395</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>17132</t>
+          <t>18135</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4496,12 +4496,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>25,32%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4516,12 +4516,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>5412</t>
+          <t>5294</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>14862</t>
+          <t>13860</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4531,12 +4531,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4551,12 +4551,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>15775</t>
+          <t>14876</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>28935</t>
+          <t>28569</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4566,12 +4566,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>20,83%</t>
         </is>
       </c>
     </row>
@@ -4594,12 +4594,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>20418</t>
+          <t>20544</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>33100</t>
+          <t>34150</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>28,68%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>46,21%</t>
+          <t>47,68%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4629,12 +4629,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>25184</t>
+          <t>25261</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>37633</t>
+          <t>37573</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4644,12 +4644,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>38,43%</t>
+          <t>38,55%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>57,43%</t>
+          <t>57,34%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>50302</t>
+          <t>49744</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>68161</t>
+          <t>68278</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>36,68%</t>
+          <t>36,27%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>49,7%</t>
+          <t>49,78%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>25114</t>
+          <t>25413</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>42945</t>
+          <t>43426</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>29009</t>
+          <t>28119</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>49167</t>
+          <t>47290</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>59632</t>
+          <t>59693</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>85971</t>
+          <t>85310</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,9%</t>
         </is>
       </c>
     </row>
@@ -4937,12 +4937,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>38837</t>
+          <t>38166</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>60088</t>
+          <t>58521</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4952,12 +4952,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4972,12 +4972,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>50286</t>
+          <t>49414</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>74301</t>
+          <t>72484</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4987,12 +4987,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>92859</t>
+          <t>94404</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>126194</t>
+          <t>125138</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5022,12 +5022,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,12%</t>
         </is>
       </c>
     </row>
@@ -5050,12 +5050,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>99702</t>
+          <t>99538</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>130883</t>
+          <t>129167</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5065,12 +5065,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>98171</t>
+          <t>99072</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>129608</t>
+          <t>132045</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>205950</t>
+          <t>208919</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>252175</t>
+          <t>250152</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>20,23%</t>
         </is>
       </c>
     </row>
@@ -5163,12 +5163,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>105529</t>
+          <t>106469</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>136962</t>
+          <t>138726</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5178,12 +5178,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>23,22%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5198,12 +5198,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>128001</t>
+          <t>129428</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>161792</t>
+          <t>162601</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>244482</t>
+          <t>244292</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>289726</t>
+          <t>289415</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>23,41%</t>
         </is>
       </c>
     </row>
@@ -5276,12 +5276,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>261453</t>
+          <t>259011</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>301136</t>
+          <t>297947</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5291,12 +5291,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>43,75%</t>
+          <t>43,34%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>50,39%</t>
+          <t>49,86%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5311,12 +5311,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>260018</t>
+          <t>260970</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>301462</t>
+          <t>299951</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5326,12 +5326,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>40,69%</t>
+          <t>40,84%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>47,18%</t>
+          <t>46,94%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5346,12 +5346,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>531635</t>
+          <t>533393</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>587931</t>
+          <t>588675</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5361,12 +5361,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>42,99%</t>
+          <t>43,14%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>47,55%</t>
+          <t>47,61%</t>
         </is>
       </c>
     </row>
@@ -5745,7 +5745,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1826</t>
+          <t>2708</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5760,7 +5760,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5780,7 +5780,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4440</t>
+          <t>4479</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5795,7 +5795,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5815,7 +5815,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5083</t>
+          <t>4353</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>2,65%</t>
         </is>
       </c>
     </row>
@@ -5853,12 +5853,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1479</t>
+          <t>1801</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8479</t>
+          <t>8191</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5868,12 +5868,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5888,12 +5888,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1195</t>
+          <t>1198</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7021</t>
+          <t>6769</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5908,7 +5908,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5923,12 +5923,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3556</t>
+          <t>3789</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>12999</t>
+          <t>12129</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,37%</t>
         </is>
       </c>
     </row>
@@ -5966,12 +5966,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3564</t>
+          <t>3487</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12233</t>
+          <t>12132</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5981,12 +5981,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6001,12 +6001,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>8967</t>
+          <t>9349</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>19531</t>
+          <t>19887</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>14810</t>
+          <t>14913</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>28825</t>
+          <t>28999</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,63%</t>
         </is>
       </c>
     </row>
@@ -6079,12 +6079,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7299</t>
+          <t>7462</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18040</t>
+          <t>18387</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6094,12 +6094,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6114,12 +6114,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8348</t>
+          <t>8168</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19133</t>
+          <t>18829</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17843</t>
+          <t>18377</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>32619</t>
+          <t>32634</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,84%</t>
         </is>
       </c>
     </row>
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>54292</t>
+          <t>54512</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>68014</t>
+          <t>67559</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6207,12 +6207,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>63,8%</t>
+          <t>64,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>79,93%</t>
+          <t>79,4%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>40546</t>
+          <t>40805</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>54294</t>
+          <t>55110</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>51,08%</t>
+          <t>51,4%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>68,4%</t>
+          <t>69,42%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>99673</t>
+          <t>98215</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>119140</t>
+          <t>118427</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>60,6%</t>
+          <t>59,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>72,44%</t>
+          <t>72,0%</t>
         </is>
       </c>
     </row>
@@ -6422,12 +6422,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>581</t>
+          <t>584</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5077</t>
+          <t>5294</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6442,7 +6442,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6457,12 +6457,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>677</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6744</t>
+          <t>6144</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1872</t>
+          <t>1959</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9025</t>
+          <t>9050</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,17%</t>
         </is>
       </c>
     </row>
@@ -6535,12 +6535,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1424</t>
+          <t>1445</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8130</t>
+          <t>8154</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6550,12 +6550,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6570,12 +6570,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>690</t>
+          <t>866</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6455</t>
+          <t>7505</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>3369</t>
+          <t>3134</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>11959</t>
+          <t>11498</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,57%</t>
         </is>
       </c>
     </row>
@@ -6648,12 +6648,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7437</t>
+          <t>8030</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>18125</t>
+          <t>19305</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8637</t>
+          <t>8872</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>20094</t>
+          <t>20326</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>19381</t>
+          <t>18657</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>34812</t>
+          <t>33707</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>19,25%</t>
         </is>
       </c>
     </row>
@@ -6761,12 +6761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10203</t>
+          <t>10756</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22171</t>
+          <t>22949</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10259</t>
+          <t>9957</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>22502</t>
+          <t>21228</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6811,12 +6811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>24113</t>
+          <t>23931</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>40963</t>
+          <t>40430</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>23,09%</t>
         </is>
       </c>
     </row>
@@ -6874,12 +6874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>43721</t>
+          <t>43765</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>58667</t>
+          <t>58168</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>51,05%</t>
+          <t>51,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>68,51%</t>
+          <t>67,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>47275</t>
+          <t>47360</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>62584</t>
+          <t>62406</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6924,12 +6924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>52,86%</t>
+          <t>52,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>69,98%</t>
+          <t>69,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>96353</t>
+          <t>96131</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>116645</t>
+          <t>116805</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>55,04%</t>
+          <t>54,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>66,63%</t>
+          <t>66,72%</t>
         </is>
       </c>
     </row>
@@ -7104,12 +7104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>682</t>
+          <t>697</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6014</t>
+          <t>6033</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7144,7 +7144,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4598</t>
+          <t>4115</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7159,7 +7159,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1346</t>
+          <t>1365</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7917</t>
+          <t>7802</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7189,12 +7189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,88%</t>
         </is>
       </c>
     </row>
@@ -7217,12 +7217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>692</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6577</t>
+          <t>6330</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7252,12 +7252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2547</t>
+          <t>2544</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9469</t>
+          <t>9604</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7272,7 +7272,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7287,12 +7287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3974</t>
+          <t>3998</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>13168</t>
+          <t>13269</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7302,12 +7302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,3%</t>
         </is>
       </c>
     </row>
@@ -7330,12 +7330,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>11326</t>
+          <t>11881</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>24409</t>
+          <t>24455</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>30,68%</t>
+          <t>30,74%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>6262</t>
+          <t>6153</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>15657</t>
+          <t>16423</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>20442</t>
+          <t>20567</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>37457</t>
+          <t>37726</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7415,12 +7415,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>23,61%</t>
         </is>
       </c>
     </row>
@@ -7443,12 +7443,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8884</t>
+          <t>8549</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>20577</t>
+          <t>19406</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7478,12 +7478,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8592</t>
+          <t>9075</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>19194</t>
+          <t>19702</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7493,12 +7493,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7513,12 +7513,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>19080</t>
+          <t>19146</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>33885</t>
+          <t>34562</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7528,12 +7528,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>21,63%</t>
         </is>
       </c>
     </row>
@@ -7556,12 +7556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>35311</t>
+          <t>36097</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>50609</t>
+          <t>50535</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7571,12 +7571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>44,38%</t>
+          <t>45,37%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>63,61%</t>
+          <t>63,52%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7591,12 +7591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>42877</t>
+          <t>41370</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>56172</t>
+          <t>56049</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7606,12 +7606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>53,44%</t>
+          <t>51,57%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>70,02%</t>
+          <t>69,86%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7626,12 +7626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>83323</t>
+          <t>81980</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>103384</t>
+          <t>102279</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7641,12 +7641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>52,15%</t>
+          <t>51,31%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>64,7%</t>
+          <t>64,01%</t>
         </is>
       </c>
     </row>
@@ -7786,12 +7786,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1340</t>
+          <t>1347</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7447</t>
+          <t>7542</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3381</t>
+          <t>3344</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>12659</t>
+          <t>11704</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7836,12 +7836,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6019</t>
+          <t>6016</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>15953</t>
+          <t>16594</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7876,7 +7876,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,22%</t>
         </is>
       </c>
     </row>
@@ -7899,12 +7899,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>9423</t>
+          <t>9520</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>21243</t>
+          <t>21566</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7914,12 +7914,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7934,12 +7934,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>11921</t>
+          <t>11868</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>24761</t>
+          <t>24775</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7949,7 +7949,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -7969,12 +7969,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>24294</t>
+          <t>24751</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>41411</t>
+          <t>42650</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7984,12 +7984,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,84%</t>
         </is>
       </c>
     </row>
@@ -8012,12 +8012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>23630</t>
+          <t>23555</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>39565</t>
+          <t>40476</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8027,12 +8027,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8047,12 +8047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>25004</t>
+          <t>24556</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>41758</t>
+          <t>42598</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8062,12 +8062,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8082,12 +8082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>53070</t>
+          <t>52474</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>77646</t>
+          <t>76966</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8097,12 +8097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,56%</t>
         </is>
       </c>
     </row>
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>23367</t>
+          <t>23019</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>39868</t>
+          <t>40020</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8140,12 +8140,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8160,12 +8160,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>24018</t>
+          <t>22978</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>41934</t>
+          <t>40681</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8175,12 +8175,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8195,12 +8195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>50663</t>
+          <t>51232</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>75731</t>
+          <t>74602</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8210,12 +8210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>18,96%</t>
         </is>
       </c>
     </row>
@@ -8238,12 +8238,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>93538</t>
+          <t>94373</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>116207</t>
+          <t>116234</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>50,5%</t>
+          <t>50,95%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>62,74%</t>
+          <t>62,76%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8273,12 +8273,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>108288</t>
+          <t>108012</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>131127</t>
+          <t>130876</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8288,12 +8288,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>51,98%</t>
+          <t>51,85%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>62,94%</t>
+          <t>62,82%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8308,12 +8308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>207386</t>
+          <t>208540</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>241881</t>
+          <t>239472</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8323,12 +8323,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>52,7%</t>
+          <t>52,99%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>61,46%</t>
+          <t>60,85%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1439</t>
+          <t>1467</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>8137</t>
+          <t>8138</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -8483,7 +8483,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>4263</t>
+          <t>4393</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>13942</t>
+          <t>14923</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>7535</t>
+          <t>8018</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>19436</t>
+          <t>19728</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,35%</t>
         </is>
       </c>
     </row>
@@ -8581,12 +8581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>6521</t>
+          <t>6539</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>17876</t>
+          <t>18008</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8596,12 +8596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8616,12 +8616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>5048</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>14054</t>
+          <t>14443</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8631,12 +8631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -8651,12 +8651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>13369</t>
+          <t>12750</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>26979</t>
+          <t>27463</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8666,12 +8666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,23%</t>
         </is>
       </c>
     </row>
@@ -8694,12 +8694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>18196</t>
+          <t>17452</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>33452</t>
+          <t>32637</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8709,12 +8709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>23,63%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8729,12 +8729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>20482</t>
+          <t>19777</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>36324</t>
+          <t>35372</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8744,12 +8744,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>27,17%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>42182</t>
+          <t>41846</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>64320</t>
+          <t>63213</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8779,12 +8779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>23,56%</t>
         </is>
       </c>
     </row>
@@ -8807,12 +8807,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>13429</t>
+          <t>13520</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>26972</t>
+          <t>27022</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8822,12 +8822,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8842,12 +8842,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>14582</t>
+          <t>15229</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>28693</t>
+          <t>29053</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8857,12 +8857,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>31534</t>
+          <t>30633</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>52712</t>
+          <t>51368</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8892,12 +8892,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,14%</t>
         </is>
       </c>
     </row>
@@ -8920,12 +8920,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>68708</t>
+          <t>69572</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>88235</t>
+          <t>88564</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8935,12 +8935,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>49,74%</t>
+          <t>50,36%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>63,87%</t>
+          <t>64,11%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8955,12 +8955,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>54468</t>
+          <t>54920</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>73965</t>
+          <t>73600</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8970,12 +8970,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>41,83%</t>
+          <t>42,18%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>56,81%</t>
+          <t>56,52%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8990,12 +8990,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>130897</t>
+          <t>128788</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>155813</t>
+          <t>156001</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9005,12 +9005,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>48,78%</t>
+          <t>47,99%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>58,06%</t>
+          <t>58,13%</t>
         </is>
       </c>
     </row>
@@ -9155,7 +9155,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>3928</t>
+          <t>3494</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -9170,7 +9170,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>1263</t>
+          <t>1296</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>6847</t>
+          <t>7264</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1339</t>
+          <t>1332</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>7428</t>
+          <t>7534</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,46%</t>
         </is>
       </c>
     </row>
@@ -9263,12 +9263,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>2262</t>
+          <t>2241</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>9651</t>
+          <t>9327</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9278,12 +9278,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9298,12 +9298,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>4225</t>
+          <t>4273</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>13571</t>
+          <t>13382</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -9313,12 +9313,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -9333,12 +9333,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>7914</t>
+          <t>8121</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>19727</t>
+          <t>19242</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -9348,12 +9348,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>16,5%</t>
         </is>
       </c>
     </row>
@@ -9376,12 +9376,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>4321</t>
+          <t>4495</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>12918</t>
+          <t>13522</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9391,12 +9391,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>27,45%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>8049</t>
+          <t>8044</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>19393</t>
+          <t>18730</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>27,81%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>14402</t>
+          <t>14010</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>28707</t>
+          <t>27607</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -9461,12 +9461,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>23,67%</t>
         </is>
       </c>
     </row>
@@ -9489,12 +9489,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>7961</t>
+          <t>7490</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>18098</t>
+          <t>17654</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -9504,12 +9504,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>36,73%</t>
+          <t>35,83%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -9524,12 +9524,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>6028</t>
+          <t>6201</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>15548</t>
+          <t>16112</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -9539,12 +9539,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -9559,12 +9559,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>16191</t>
+          <t>16025</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>29473</t>
+          <t>30850</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -9574,12 +9574,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>26,45%</t>
         </is>
       </c>
     </row>
@@ -9602,12 +9602,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>17673</t>
+          <t>17823</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>29023</t>
+          <t>29251</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -9617,12 +9617,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>35,87%</t>
+          <t>36,18%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>58,91%</t>
+          <t>59,37%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -9637,12 +9637,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>26732</t>
+          <t>26322</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>40070</t>
+          <t>40169</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>39,69%</t>
+          <t>39,08%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>59,49%</t>
+          <t>59,64%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>47933</t>
+          <t>46743</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>65989</t>
+          <t>65220</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>41,1%</t>
+          <t>40,08%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>56,58%</t>
+          <t>55,92%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>8624</t>
+          <t>8255</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>19904</t>
+          <t>19078</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>16523</t>
+          <t>17027</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>32233</t>
+          <t>32139</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>27527</t>
+          <t>27956</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>47629</t>
+          <t>47287</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,7%</t>
         </is>
       </c>
     </row>
@@ -9945,12 +9945,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>32252</t>
+          <t>32271</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>52511</t>
+          <t>52583</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -9965,7 +9965,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -9980,12 +9980,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>36159</t>
+          <t>36249</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>57990</t>
+          <t>56721</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -9995,12 +9995,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -10015,12 +10015,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>73384</t>
+          <t>73392</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>100982</t>
+          <t>102506</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -10035,7 +10035,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>8,02%</t>
         </is>
       </c>
     </row>
@@ -10058,12 +10058,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>86595</t>
+          <t>87290</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>117025</t>
+          <t>117845</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -10073,12 +10073,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10093,12 +10093,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>94331</t>
+          <t>94931</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>125999</t>
+          <t>127011</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>192222</t>
+          <t>191483</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>235993</t>
+          <t>234197</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>18,33%</t>
         </is>
       </c>
     </row>
@@ -10171,12 +10171,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>88501</t>
+          <t>88306</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>121058</t>
+          <t>118354</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -10186,12 +10186,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -10206,12 +10206,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>91953</t>
+          <t>91513</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>123474</t>
+          <t>123101</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -10221,12 +10221,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>186204</t>
+          <t>187193</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>230270</t>
+          <t>231349</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>18,1%</t>
         </is>
       </c>
     </row>
@@ -10284,12 +10284,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>343706</t>
+          <t>343034</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>383750</t>
+          <t>382814</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -10299,12 +10299,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>55,18%</t>
+          <t>55,07%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>61,61%</t>
+          <t>61,46%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -10319,12 +10319,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>347853</t>
+          <t>348346</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>390333</t>
+          <t>389171</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -10334,12 +10334,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>53,11%</t>
+          <t>53,19%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>59,6%</t>
+          <t>59,42%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>703741</t>
+          <t>703137</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>763619</t>
+          <t>761109</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>55,07%</t>
+          <t>55,03%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>59,76%</t>
+          <t>59,56%</t>
         </is>
       </c>
     </row>
@@ -10753,7 +10753,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2632</t>
+          <t>3258</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10768,7 +10768,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10788,7 +10788,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>2541</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10803,7 +10803,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10823,7 +10823,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4441</t>
+          <t>4152</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10838,7 +10838,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,52%</t>
         </is>
       </c>
     </row>
@@ -10861,12 +10861,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1993</t>
+          <t>1856</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9368</t>
+          <t>9360</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10876,12 +10876,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10896,12 +10896,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>586</t>
+          <t>596</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5364</t>
+          <t>6104</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10911,12 +10911,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10931,12 +10931,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3334</t>
+          <t>3291</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>12266</t>
+          <t>12265</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10946,7 +10946,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -10974,12 +10974,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6268</t>
+          <t>6352</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>16274</t>
+          <t>16653</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10989,12 +10989,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11009,12 +11009,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>8902</t>
+          <t>8956</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>20100</t>
+          <t>20248</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11024,12 +11024,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11044,12 +11044,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>17459</t>
+          <t>17309</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>32166</t>
+          <t>32615</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11059,12 +11059,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>19,83%</t>
         </is>
       </c>
     </row>
@@ -11087,12 +11087,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13711</t>
+          <t>14543</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26239</t>
+          <t>26359</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11102,12 +11102,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,91%</t>
+          <t>35,07%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11122,12 +11122,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14178</t>
+          <t>14739</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27321</t>
+          <t>27111</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11137,12 +11137,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>30,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11157,12 +11157,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>31317</t>
+          <t>32099</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>49697</t>
+          <t>49319</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>29,99%</t>
         </is>
       </c>
     </row>
@@ -11200,12 +11200,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>32669</t>
+          <t>32937</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>47054</t>
+          <t>46382</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11215,12 +11215,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>43,46%</t>
+          <t>43,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>62,6%</t>
+          <t>61,71%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11235,12 +11235,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>43907</t>
+          <t>44377</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>60049</t>
+          <t>58617</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>49,18%</t>
+          <t>49,7%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>67,25%</t>
+          <t>65,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11270,12 +11270,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>82807</t>
+          <t>81518</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>103119</t>
+          <t>102261</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>50,35%</t>
+          <t>49,57%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>62,71%</t>
+          <t>62,18%</t>
         </is>
       </c>
     </row>
@@ -11430,12 +11430,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>575</t>
+          <t>570</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5774</t>
+          <t>5884</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11445,12 +11445,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11470,7 +11470,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5126</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11485,7 +11485,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11500,12 +11500,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1517</t>
+          <t>1667</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8802</t>
+          <t>8649</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11515,12 +11515,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,3%</t>
         </is>
       </c>
     </row>
@@ -11543,12 +11543,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1382</t>
+          <t>1710</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8249</t>
+          <t>8675</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11558,12 +11558,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11578,12 +11578,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>712</t>
+          <t>705</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7033</t>
+          <t>7136</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11593,12 +11593,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11613,12 +11613,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>3464</t>
+          <t>3366</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>12281</t>
+          <t>11410</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11628,12 +11628,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>5,67%</t>
         </is>
       </c>
     </row>
@@ -11656,12 +11656,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>10981</t>
+          <t>11261</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>23759</t>
+          <t>23498</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11671,12 +11671,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11691,12 +11691,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>11449</t>
+          <t>11682</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>23596</t>
+          <t>24058</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>25979</t>
+          <t>25410</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>42629</t>
+          <t>43137</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>21,43%</t>
         </is>
       </c>
     </row>
@@ -11769,12 +11769,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13519</t>
+          <t>14029</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26535</t>
+          <t>27403</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11784,12 +11784,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11804,12 +11804,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16414</t>
+          <t>16387</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29872</t>
+          <t>30119</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,48%</t>
+          <t>28,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>33136</t>
+          <t>33331</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>53189</t>
+          <t>52490</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>26,08%</t>
         </is>
       </c>
     </row>
@@ -11882,12 +11882,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>45810</t>
+          <t>45504</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>62072</t>
+          <t>61219</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11897,12 +11897,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>47,52%</t>
+          <t>47,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>64,39%</t>
+          <t>63,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11917,12 +11917,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>52287</t>
+          <t>52186</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>68320</t>
+          <t>68173</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>49,84%</t>
+          <t>49,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>65,13%</t>
+          <t>64,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11952,12 +11952,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>102876</t>
+          <t>102364</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>125880</t>
+          <t>125974</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>51,11%</t>
+          <t>50,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>62,53%</t>
+          <t>62,58%</t>
         </is>
       </c>
     </row>
@@ -12147,12 +12147,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>569</t>
+          <t>559</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5852</t>
+          <t>5876</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12162,12 +12162,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12182,12 +12182,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>557</t>
+          <t>564</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5909</t>
+          <t>6375</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12202,7 +12202,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>5,0%</t>
         </is>
       </c>
     </row>
@@ -12225,12 +12225,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1521</t>
+          <t>1867</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8601</t>
+          <t>7936</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12240,12 +12240,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12260,12 +12260,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2743</t>
+          <t>3251</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10660</t>
+          <t>10869</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12275,12 +12275,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6034</t>
+          <t>5776</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>15944</t>
+          <t>16396</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12310,12 +12310,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,87%</t>
         </is>
       </c>
     </row>
@@ -12338,12 +12338,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>7415</t>
+          <t>7450</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>17458</t>
+          <t>17678</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12353,12 +12353,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>30,87%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12373,12 +12373,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3803</t>
+          <t>3953</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>11449</t>
+          <t>11842</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12388,12 +12388,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12408,12 +12408,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>13213</t>
+          <t>12719</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>26472</t>
+          <t>26669</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12423,12 +12423,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,93%</t>
         </is>
       </c>
     </row>
@@ -12451,12 +12451,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6653</t>
+          <t>6980</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15945</t>
+          <t>16334</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12466,12 +12466,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>28,53%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12486,12 +12486,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>12645</t>
+          <t>12828</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>24910</t>
+          <t>24670</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12501,12 +12501,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>35,51%</t>
+          <t>35,16%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12521,12 +12521,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>21029</t>
+          <t>21874</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>36921</t>
+          <t>37772</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12536,12 +12536,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>29,64%</t>
         </is>
       </c>
     </row>
@@ -12564,12 +12564,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>24963</t>
+          <t>24376</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>36572</t>
+          <t>36505</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12579,12 +12579,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>43,6%</t>
+          <t>42,57%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>63,87%</t>
+          <t>63,75%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12599,12 +12599,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>29726</t>
+          <t>29733</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>43316</t>
+          <t>43598</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12614,12 +12614,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>42,37%</t>
+          <t>42,38%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>61,74%</t>
+          <t>62,14%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12634,12 +12634,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>57716</t>
+          <t>58736</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>76809</t>
+          <t>77351</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12649,12 +12649,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>45,3%</t>
+          <t>46,1%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>60,28%</t>
+          <t>60,71%</t>
         </is>
       </c>
     </row>
@@ -12794,12 +12794,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2106</t>
+          <t>1997</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9580</t>
+          <t>10092</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12809,12 +12809,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12829,12 +12829,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6016</t>
+          <t>5950</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>16808</t>
+          <t>16863</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12844,12 +12844,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12864,12 +12864,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>9222</t>
+          <t>9569</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>21832</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12879,12 +12879,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,34%</t>
         </is>
       </c>
     </row>
@@ -12907,12 +12907,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>8713</t>
+          <t>8244</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>19569</t>
+          <t>19170</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12922,12 +12922,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12942,12 +12942,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>11722</t>
+          <t>11338</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>25238</t>
+          <t>24339</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12957,12 +12957,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>23030</t>
+          <t>23138</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>39910</t>
+          <t>40972</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12992,12 +12992,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>10,01%</t>
         </is>
       </c>
     </row>
@@ -13020,12 +13020,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>24479</t>
+          <t>24593</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>41579</t>
+          <t>41582</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13035,7 +13035,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -13055,12 +13055,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>21196</t>
+          <t>21725</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>37745</t>
+          <t>38760</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13070,12 +13070,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13090,12 +13090,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>51455</t>
+          <t>49811</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>74723</t>
+          <t>74350</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13105,12 +13105,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,17%</t>
         </is>
       </c>
     </row>
@@ -13133,12 +13133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>41661</t>
+          <t>42319</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>61599</t>
+          <t>61646</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13148,12 +13148,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>29,66%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13168,12 +13168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>31680</t>
+          <t>32169</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>50711</t>
+          <t>50658</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13183,12 +13183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13203,12 +13203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>78220</t>
+          <t>80332</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>106642</t>
+          <t>107804</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13218,12 +13218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>26,35%</t>
         </is>
       </c>
     </row>
@@ -13246,12 +13246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>93439</t>
+          <t>93869</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>117739</t>
+          <t>115849</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13261,12 +13261,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>44,96%</t>
+          <t>45,17%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>56,65%</t>
+          <t>55,74%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13281,12 +13281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>92685</t>
+          <t>91877</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>116145</t>
+          <t>115488</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13296,12 +13296,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>46,04%</t>
+          <t>45,64%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>57,69%</t>
+          <t>57,36%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13316,12 +13316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>194317</t>
+          <t>191378</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>227197</t>
+          <t>224197</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13331,12 +13331,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>47,49%</t>
+          <t>46,77%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>55,53%</t>
+          <t>54,79%</t>
         </is>
       </c>
     </row>
@@ -13476,12 +13476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1226</t>
+          <t>1177</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>7116</t>
+          <t>7202</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13491,12 +13491,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13511,12 +13511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3216</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>11179</t>
+          <t>11021</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13526,12 +13526,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13546,12 +13546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>5663</t>
+          <t>5725</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>15601</t>
+          <t>15538</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13561,12 +13561,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,86%</t>
         </is>
       </c>
     </row>
@@ -13589,12 +13589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>4365</t>
+          <t>4477</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>12977</t>
+          <t>13439</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13624,12 +13624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>4589</t>
+          <t>5186</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>15242</t>
+          <t>15320</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13639,12 +13639,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13659,12 +13659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>11458</t>
+          <t>11883</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>24439</t>
+          <t>25008</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13674,12 +13674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,44%</t>
         </is>
       </c>
     </row>
@@ -13702,12 +13702,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>11098</t>
+          <t>11159</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>24516</t>
+          <t>24109</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13717,12 +13717,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -13737,12 +13737,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>12279</t>
+          <t>12134</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>25539</t>
+          <t>24950</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13752,12 +13752,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -13772,12 +13772,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>26762</t>
+          <t>26692</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>45426</t>
+          <t>45232</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -13787,12 +13787,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,07%</t>
         </is>
       </c>
     </row>
@@ -13815,12 +13815,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>15409</t>
+          <t>15725</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>29207</t>
+          <t>29937</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -13830,12 +13830,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -13850,12 +13850,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>17075</t>
+          <t>16386</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>32373</t>
+          <t>31863</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -13865,12 +13865,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -13885,12 +13885,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>36178</t>
+          <t>36118</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>56167</t>
+          <t>57341</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -13900,12 +13900,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>21,64%</t>
         </is>
       </c>
     </row>
@@ -13928,12 +13928,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>72002</t>
+          <t>71951</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>90851</t>
+          <t>90060</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -13943,12 +13943,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>54,77%</t>
+          <t>54,74%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>69,11%</t>
+          <t>68,51%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -13963,12 +13963,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>66459</t>
+          <t>66457</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>85494</t>
+          <t>85367</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -13983,7 +13983,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>64,01%</t>
+          <t>63,92%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -13998,12 +13998,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>142866</t>
+          <t>143955</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>169657</t>
+          <t>170185</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14013,12 +14013,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>53,91%</t>
+          <t>54,32%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>64,02%</t>
+          <t>64,22%</t>
         </is>
       </c>
     </row>
@@ -14163,7 +14163,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>3733</t>
+          <t>3082</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -14178,7 +14178,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -14193,12 +14193,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>878</t>
+          <t>895</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>7045</t>
+          <t>7816</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -14208,12 +14208,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -14228,12 +14228,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1564</t>
+          <t>1523</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>9182</t>
+          <t>8736</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -14243,12 +14243,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,17%</t>
         </is>
       </c>
     </row>
@@ -14271,12 +14271,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>1240</t>
+          <t>1253</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>8736</t>
+          <t>8330</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -14286,12 +14286,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -14306,12 +14306,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>691</t>
+          <t>686</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>6534</t>
+          <t>5789</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -14321,12 +14321,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -14341,12 +14341,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>3004</t>
+          <t>2913</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>11507</t>
+          <t>12000</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,85%</t>
         </is>
       </c>
     </row>
@@ -14384,12 +14384,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>7005</t>
+          <t>6544</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>17387</t>
+          <t>16780</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -14399,12 +14399,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>29,54%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -14419,12 +14419,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>5339</t>
+          <t>5517</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>15005</t>
+          <t>14633</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -14434,12 +14434,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -14454,12 +14454,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>14162</t>
+          <t>14044</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>28096</t>
+          <t>27869</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -14469,12 +14469,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>22,88%</t>
         </is>
       </c>
     </row>
@@ -14497,12 +14497,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>10063</t>
+          <t>10006</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>20788</t>
+          <t>20542</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -14512,12 +14512,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>36,6%</t>
+          <t>36,17%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -14532,12 +14532,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>14638</t>
+          <t>14972</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>27534</t>
+          <t>27360</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -14547,12 +14547,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>42,35%</t>
+          <t>42,08%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -14567,12 +14567,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>28393</t>
+          <t>27366</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>45535</t>
+          <t>44417</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -14582,12 +14582,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>37,38%</t>
+          <t>36,46%</t>
         </is>
       </c>
     </row>
@@ -14610,12 +14610,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>19520</t>
+          <t>19867</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>31981</t>
+          <t>32534</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -14625,12 +14625,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>34,36%</t>
+          <t>34,98%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>56,3%</t>
+          <t>57,28%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -14645,12 +14645,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>22507</t>
+          <t>23110</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>36269</t>
+          <t>35915</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -14660,12 +14660,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>35,55%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>55,79%</t>
+          <t>55,24%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -14680,12 +14680,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>45553</t>
+          <t>45683</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>64951</t>
+          <t>64144</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -14695,12 +14695,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>37,4%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>53,32%</t>
+          <t>52,66%</t>
         </is>
       </c>
     </row>
@@ -14840,12 +14840,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>7650</t>
+          <t>7550</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>18488</t>
+          <t>18182</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -14855,12 +14855,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -14875,12 +14875,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>16796</t>
+          <t>16839</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>32928</t>
+          <t>33378</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -14890,12 +14890,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -14910,12 +14910,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>26520</t>
+          <t>27765</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>46525</t>
+          <t>46875</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -14925,12 +14925,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,64%</t>
         </is>
       </c>
     </row>
@@ -14953,12 +14953,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>28979</t>
+          <t>29504</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>48893</t>
+          <t>46931</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -14968,12 +14968,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -14988,12 +14988,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>29273</t>
+          <t>30694</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>48543</t>
+          <t>50860</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -15023,12 +15023,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>64760</t>
+          <t>65172</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>92861</t>
+          <t>91234</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -15038,12 +15038,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,08%</t>
         </is>
       </c>
     </row>
@@ -15066,12 +15066,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>84977</t>
+          <t>85938</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>114354</t>
+          <t>115791</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -15081,12 +15081,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -15101,12 +15101,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>81246</t>
+          <t>81322</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>111045</t>
+          <t>111384</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -15116,12 +15116,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -15136,12 +15136,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>174273</t>
+          <t>173609</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>216292</t>
+          <t>216588</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,8%</t>
         </is>
       </c>
     </row>
@@ -15179,12 +15179,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>122474</t>
+          <t>121889</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>155565</t>
+          <t>155347</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -15194,12 +15194,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -15214,12 +15214,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>129032</t>
+          <t>129857</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>165217</t>
+          <t>165970</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -15229,12 +15229,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -15249,12 +15249,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>261150</t>
+          <t>260523</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>309497</t>
+          <t>310851</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -15264,12 +15264,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>24,11%</t>
         </is>
       </c>
     </row>
@@ -15292,12 +15292,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>317117</t>
+          <t>315746</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>357072</t>
+          <t>356809</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -15307,12 +15307,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>50,75%</t>
+          <t>50,53%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>57,14%</t>
+          <t>57,1%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -15327,12 +15327,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>336881</t>
+          <t>339244</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>378374</t>
+          <t>381238</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -15342,12 +15342,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>50,72%</t>
+          <t>51,07%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>56,96%</t>
+          <t>57,39%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -15362,12 +15362,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>665620</t>
+          <t>665885</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>724051</t>
+          <t>726300</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -15377,12 +15377,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>51,63%</t>
+          <t>51,65%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>56,17%</t>
+          <t>56,34%</t>
         </is>
       </c>
     </row>
